--- a/backend/data/financials_by_company/0670.HK.xlsx
+++ b/backend/data/financials_by_company/0670.HK.xlsx
@@ -5215,10 +5215,8 @@
           <t>Shanghai</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>201100</t>
-        </is>
+      <c r="D2" t="n">
+        <v>201100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -5345,7 +5343,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AM2" t="n">
